--- a/Synthesis.xlsx
+++ b/Synthesis.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0-DOCUMENTS\博士\0-AI真实性综述\投稿-1\v3.0大稿子\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0-DOCUMENTS\博士\0-AI真实性综述\投稿-1\v3.0大稿子\Supplementary materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3952E6-3CB7-4196-85E6-E9E815538AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -17,7 +17,20 @@
     <sheet name="Code Defination" sheetId="3" r:id="rId2"/>
     <sheet name="Analysis Process" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -470,30 +483,19 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -509,12 +511,123 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="22">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -533,12 +646,97 @@
     </dxf>
     <dxf>
       <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -654,183 +852,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -838,15 +860,6 @@
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -862,40 +875,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ThemeSynthesis" displayName="ThemeSynthesis" ref="A5:H9" totalsRowShown="0" headerRowDxfId="20" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ThemeSynthesis" displayName="ThemeSynthesis" ref="A5:H9" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Theme code" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Analytical theme" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Contributing categories/codes" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Narrative synthesis finding" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Number of contributing studies" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Contributing studies" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Key boundary conditions or tensions" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Confidence interpretation" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Theme code" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Analytical theme" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Contributing categories/codes" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Narrative synthesis finding" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Number of contributing studies" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Contributing studies" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Key boundary conditions or tensions" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Confidence interpretation" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CodingFramework" displayName="CodingFramework" ref="A5:D15" totalsRowShown="0" headerRowDxfId="1" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CodingFramework" displayName="CodingFramework" ref="A5:D15" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Code" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Level" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Label" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Operational definition" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Code" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Level" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Label" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Operational definition" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AnalysisProcess" displayName="AnalysisProcess" ref="A5:D11" totalsRowShown="0" headerRowDxfId="0" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AnalysisProcess" displayName="AnalysisProcess" ref="A5:D11" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Stage" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Phase" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Procedure" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Output retained" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Stage" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Phase" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Procedure" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Output retained" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1138,16 +1151,16 @@
       <c r="AA1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="17.5">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1169,16 +1182,16 @@
       <c r="AA2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="32" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1274,28 +1287,28 @@
       <c r="AA5" s="1"/>
     </row>
     <row r="6" spans="1:27" ht="93">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="10">
         <v>9</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="1"/>
@@ -1319,28 +1332,28 @@
       <c r="AA6" s="1"/>
     </row>
     <row r="7" spans="1:27" ht="108.5">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="12">
         <v>11</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="11" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="1"/>
@@ -1364,28 +1377,28 @@
       <c r="AA7" s="1"/>
     </row>
     <row r="8" spans="1:27" ht="93">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="10">
         <v>15</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="1"/>
@@ -1409,28 +1422,28 @@
       <c r="AA8" s="1"/>
     </row>
     <row r="9" spans="1:27" ht="79" customHeight="1">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="12">
         <v>10</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="11" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="1"/>
@@ -3189,26 +3202,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="17.5">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="3" spans="1:4" ht="32" customHeight="1">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="1:4" ht="32.5" customHeight="1">
       <c r="A5" s="4" t="s">
@@ -3225,180 +3238,180 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.5">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="15" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.5">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.5">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.5">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.5">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="15" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="31">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="15" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="31">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="15" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="31">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="46.5">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.5">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="17" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3425,26 +3438,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="17.5">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="3" spans="1:4" ht="32" customHeight="1">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="1:4" ht="25.5" customHeight="1">
       <c r="A5" s="4" t="s">
@@ -3461,148 +3474,148 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="31">
-      <c r="A6" s="19">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="15" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="31">
-      <c r="A7" s="19">
+      <c r="A7" s="14">
         <v>2</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="15" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.5">
-      <c r="A8" s="19">
+      <c r="A8" s="14">
         <v>3</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="15" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.5">
-      <c r="A9" s="19">
+      <c r="A9" s="14">
         <v>4</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="15" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.5">
-      <c r="A10" s="19">
+      <c r="A10" s="14">
         <v>5</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="15" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.5">
-      <c r="A11" s="21">
+      <c r="A11" s="16">
         <v>6</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="17" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.5">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
     </row>
     <row r="13" spans="1:4" ht="15.5">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
     </row>
     <row r="14" spans="1:4" ht="15.5">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
     </row>
     <row r="15" spans="1:4" ht="15.5">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
     </row>
     <row r="16" spans="1:4" ht="15.5">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4" ht="15.5">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4" ht="15.5">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
     </row>
     <row r="19" spans="1:4" ht="15.5">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
